--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -2134,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -3095,71 +3095,60 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="n"/>
-      <c r="D18" s="57" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="57" t="n"/>
-      <c r="D19" s="57" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="57" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Test17</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>roh@sgmco.cl</t>
         </is>
       </c>
-      <c r="C21" s="60" t="n">
+      <c r="C18" s="60" t="n">
         <v>46119</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>macOS</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>WorkM5</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>(10c-4.61GHz)</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>ARM</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>ARM64 (gfortran)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>MacBook Pro Laptop</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Native ARM64; usgt_180_arm compiled with gfortran via Homebrew GCC</t>
         </is>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
     <col width="12.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -952,6 +952,16 @@
           <t>M5</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>M3 Max</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1044,6 +1054,16 @@
           <t>WorkM5</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>WorkM3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SGM035</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
@@ -1136,6 +1156,16 @@
           <t>(10c-4.61GHz)</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>(16c-4.05 GHz)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>(10c-4.51 GHz)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
@@ -1226,6 +1256,16 @@
       <c r="R4" t="inlineStr">
         <is>
           <t>Test17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Test18</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Test19</t>
         </is>
       </c>
     </row>
@@ -1284,6 +1324,9 @@
       <c r="R5" t="n">
         <v>3.478</v>
       </c>
+      <c r="S5" t="n">
+        <v>4.7354</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="54">
       <c r="A6" s="17" t="n">
@@ -1340,6 +1383,9 @@
       <c r="R6" t="n">
         <v>3.7012</v>
       </c>
+      <c r="S6" t="n">
+        <v>4.7135</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="54">
       <c r="A7" s="17" t="n">
@@ -1396,6 +1442,9 @@
       <c r="R7" t="n">
         <v>3.9802</v>
       </c>
+      <c r="S7" t="n">
+        <v>4.7988</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="54">
       <c r="A8" s="17" t="n">
@@ -1452,6 +1501,9 @@
       <c r="R8" t="n">
         <v>4.3041</v>
       </c>
+      <c r="S8" t="n">
+        <v>4.7793</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="54">
       <c r="A9" s="17" t="n">
@@ -1508,6 +1560,9 @@
       <c r="R9" t="n">
         <v>4.636</v>
       </c>
+      <c r="S9" t="n">
+        <v>4.7951</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="54">
       <c r="A10" s="17" t="n">
@@ -1562,6 +1617,9 @@
       <c r="R10" t="n">
         <v>5.016</v>
       </c>
+      <c r="S10" t="n">
+        <v>4.8687</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="54">
       <c r="A11" s="18" t="n">
@@ -1618,6 +1676,9 @@
       <c r="R11" t="n">
         <v>5.4074</v>
       </c>
+      <c r="S11" t="n">
+        <v>5.0869</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="54">
       <c r="A12" s="17" t="n">
@@ -1674,6 +1735,9 @@
       <c r="R12" t="n">
         <v>5.6641</v>
       </c>
+      <c r="S12" t="n">
+        <v>5.2382</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="54">
       <c r="A13" s="17" t="n">
@@ -1728,6 +1792,9 @@
       <c r="R13" t="n">
         <v>6.2495</v>
       </c>
+      <c r="S13" t="n">
+        <v>5.8334</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="54">
       <c r="A14" s="17" t="n">
@@ -1782,6 +1849,9 @@
       <c r="R14" t="n">
         <v>6.8451</v>
       </c>
+      <c r="S14" t="n">
+        <v>6.321</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="54">
       <c r="A15" s="17" t="n">
@@ -1839,6 +1909,9 @@
       <c r="R15" t="n">
         <v>7.7447</v>
       </c>
+      <c r="S15" t="n">
+        <v>7.181</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="54">
       <c r="A16" s="17" t="n">
@@ -1896,6 +1969,9 @@
       <c r="R16" t="n">
         <v>8.3064</v>
       </c>
+      <c r="S16" t="n">
+        <v>7.6501</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="54">
       <c r="A17" s="17" t="n">
@@ -1951,6 +2027,9 @@
       <c r="R17" t="n">
         <v>9.1073</v>
       </c>
+      <c r="S17" t="n">
+        <v>8.379799999999999</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="54">
       <c r="A18" s="17" t="n">
@@ -2008,6 +2087,9 @@
       <c r="R18" t="n">
         <v>9.8291</v>
       </c>
+      <c r="S18" t="n">
+        <v>9.0161</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="54">
       <c r="A19" s="17" t="n">
@@ -2065,6 +2147,9 @@
       <c r="R19" t="n">
         <v>10.8483</v>
       </c>
+      <c r="S19" t="n">
+        <v>9.616099999999999</v>
+      </c>
     </row>
     <row r="20" customFormat="1" s="54">
       <c r="A20" s="17" t="n">
@@ -2120,6 +2205,12 @@
       </c>
       <c r="R20" t="n">
         <v>11.3681</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10.1899</v>
+      </c>
+      <c r="T20" t="n">
+        <v>13.6628</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -3151,6 +3242,126 @@
       <c r="L18" t="inlineStr">
         <is>
           <t>Native ARM64; usgt_180_arm compiled with gfortran via Homebrew GCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Test18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>roh@sgmco.cl</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="n">
+        <v>46129</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M3 Max</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>WorkM3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>(16c-4.05 GHz)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ARM64 (gfortran)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>MacBook Pro Laptop</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Native ARM64; usgt_180_arm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Test19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>roh@sgmco.cl</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="n">
+        <v>46129</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SGM035</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>(10c-4.51 GHz)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ARM64 (gfortran)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Mac Mini</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Partial — 16-agent run only (old agent_runtimes format); full sweep pending</t>
         </is>
       </c>
     </row>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -1327,6 +1327,9 @@
       <c r="S5" t="n">
         <v>4.7354</v>
       </c>
+      <c r="T5" t="n">
+        <v>3.6019</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="54">
       <c r="A6" s="17" t="n">
@@ -1386,6 +1389,9 @@
       <c r="S6" t="n">
         <v>4.7135</v>
       </c>
+      <c r="T6" t="n">
+        <v>3.9379</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="54">
       <c r="A7" s="17" t="n">
@@ -1445,6 +1451,9 @@
       <c r="S7" t="n">
         <v>4.7988</v>
       </c>
+      <c r="T7" t="n">
+        <v>4.128</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="54">
       <c r="A8" s="17" t="n">
@@ -1504,6 +1513,9 @@
       <c r="S8" t="n">
         <v>4.7793</v>
       </c>
+      <c r="T8" t="n">
+        <v>4.5206</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="54">
       <c r="A9" s="17" t="n">
@@ -1563,6 +1575,9 @@
       <c r="S9" t="n">
         <v>4.7951</v>
       </c>
+      <c r="T9" t="n">
+        <v>5.052</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="54">
       <c r="A10" s="17" t="n">
@@ -1620,6 +1635,9 @@
       <c r="S10" t="n">
         <v>4.8687</v>
       </c>
+      <c r="T10" t="n">
+        <v>5.5552</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="54">
       <c r="A11" s="18" t="n">
@@ -1679,6 +1697,9 @@
       <c r="S11" t="n">
         <v>5.0869</v>
       </c>
+      <c r="T11" t="n">
+        <v>6.1346</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="54">
       <c r="A12" s="17" t="n">
@@ -1738,6 +1759,9 @@
       <c r="S12" t="n">
         <v>5.2382</v>
       </c>
+      <c r="T12" t="n">
+        <v>6.8325</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="54">
       <c r="A13" s="17" t="n">
@@ -1795,6 +1819,9 @@
       <c r="S13" t="n">
         <v>5.8334</v>
       </c>
+      <c r="T13" t="n">
+        <v>7.5822</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="54">
       <c r="A14" s="17" t="n">
@@ -1852,6 +1879,9 @@
       <c r="S14" t="n">
         <v>6.321</v>
       </c>
+      <c r="T14" t="n">
+        <v>8.4147</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="54">
       <c r="A15" s="17" t="n">
@@ -1912,6 +1942,9 @@
       <c r="S15" t="n">
         <v>7.181</v>
       </c>
+      <c r="T15" t="n">
+        <v>9.288600000000001</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="54">
       <c r="A16" s="17" t="n">
@@ -1972,6 +2005,9 @@
       <c r="S16" t="n">
         <v>7.6501</v>
       </c>
+      <c r="T16" t="n">
+        <v>10.1908</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="54">
       <c r="A17" s="17" t="n">
@@ -2030,6 +2066,9 @@
       <c r="S17" t="n">
         <v>8.379799999999999</v>
       </c>
+      <c r="T17" t="n">
+        <v>11.0448</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="54">
       <c r="A18" s="17" t="n">
@@ -2090,6 +2129,9 @@
       <c r="S18" t="n">
         <v>9.0161</v>
       </c>
+      <c r="T18" t="n">
+        <v>11.9249</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="54">
       <c r="A19" s="17" t="n">
@@ -2149,6 +2191,9 @@
       </c>
       <c r="S19" t="n">
         <v>9.616099999999999</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12.7899</v>
       </c>
     </row>
     <row r="20" customFormat="1" s="54">
@@ -3361,7 +3406,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Partial — 16-agent run only (old agent_runtimes format); full sweep pending</t>
+          <t>Native ARM64; usgt_180_arm compiled with gfortran via Homebrew GCC</t>
         </is>
       </c>
     </row>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -279,7 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -441,6 +442,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
     <col width="12.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -962,6 +964,11 @@
           <t>M4</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>M3 Max</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1064,6 +1071,11 @@
           <t>SGM035</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>WorkM3</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
@@ -1166,6 +1178,11 @@
           <t>(10c-4.51 GHz)</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>(16c-4.05 GHz)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
@@ -1266,6 +1283,11 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>Test19</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Test20</t>
         </is>
       </c>
     </row>
@@ -1330,6 +1352,9 @@
       <c r="T5" t="n">
         <v>3.6019</v>
       </c>
+      <c r="U5" t="n">
+        <v>5.709317</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="54">
       <c r="A6" s="17" t="n">
@@ -1392,6 +1417,9 @@
       <c r="T6" t="n">
         <v>3.9379</v>
       </c>
+      <c r="U6" t="n">
+        <v>5.7639</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="54">
       <c r="A7" s="17" t="n">
@@ -1454,6 +1482,9 @@
       <c r="T7" t="n">
         <v>4.128</v>
       </c>
+      <c r="U7" t="n">
+        <v>6.011217</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="54">
       <c r="A8" s="17" t="n">
@@ -1516,6 +1547,9 @@
       <c r="T8" t="n">
         <v>4.5206</v>
       </c>
+      <c r="U8" t="n">
+        <v>5.951067</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="54">
       <c r="A9" s="17" t="n">
@@ -1578,6 +1612,9 @@
       <c r="T9" t="n">
         <v>5.052</v>
       </c>
+      <c r="U9" t="n">
+        <v>5.9857</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="54">
       <c r="A10" s="17" t="n">
@@ -1638,6 +1675,9 @@
       <c r="T10" t="n">
         <v>5.5552</v>
       </c>
+      <c r="U10" t="n">
+        <v>6.013667</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="54">
       <c r="A11" s="18" t="n">
@@ -1700,6 +1740,9 @@
       <c r="T11" t="n">
         <v>6.1346</v>
       </c>
+      <c r="U11" t="n">
+        <v>6.130617</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="54">
       <c r="A12" s="17" t="n">
@@ -1762,6 +1805,9 @@
       <c r="T12" t="n">
         <v>6.8325</v>
       </c>
+      <c r="U12" t="n">
+        <v>6.303217</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="54">
       <c r="A13" s="17" t="n">
@@ -1822,6 +1868,9 @@
       <c r="T13" t="n">
         <v>7.5822</v>
       </c>
+      <c r="U13" t="n">
+        <v>6.508417</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="54">
       <c r="A14" s="17" t="n">
@@ -1882,6 +1931,9 @@
       <c r="T14" t="n">
         <v>8.4147</v>
       </c>
+      <c r="U14" t="n">
+        <v>6.8757</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="54">
       <c r="A15" s="17" t="n">
@@ -1945,6 +1997,9 @@
       <c r="T15" t="n">
         <v>9.288600000000001</v>
       </c>
+      <c r="U15" t="n">
+        <v>7.6243</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="54">
       <c r="A16" s="17" t="n">
@@ -2008,6 +2063,9 @@
       <c r="T16" t="n">
         <v>10.1908</v>
       </c>
+      <c r="U16" t="n">
+        <v>8.267683</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="54">
       <c r="A17" s="17" t="n">
@@ -2069,6 +2127,9 @@
       <c r="T17" t="n">
         <v>11.0448</v>
       </c>
+      <c r="U17" t="n">
+        <v>8.765833000000001</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="54">
       <c r="A18" s="17" t="n">
@@ -2132,6 +2193,9 @@
       <c r="T18" t="n">
         <v>11.9249</v>
       </c>
+      <c r="U18" t="n">
+        <v>9.445633000000001</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="54">
       <c r="A19" s="17" t="n">
@@ -2195,6 +2259,9 @@
       <c r="T19" t="n">
         <v>12.7899</v>
       </c>
+      <c r="U19" t="n">
+        <v>10.121533</v>
+      </c>
     </row>
     <row r="20" customFormat="1" s="54">
       <c r="A20" s="17" t="n">
@@ -2256,6 +2323,9 @@
       </c>
       <c r="T20" t="n">
         <v>13.6628</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10.707367</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -3407,6 +3477,66 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Native ARM64; usgt_180_arm compiled with gfortran via Homebrew GCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Test20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>roh@sgmco.cl</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="n">
+        <v>46131</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>M3 Max</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>WorkM3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>(16c-4.05 GHz)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>x86 (ifort) via Rosetta 2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MacBook Pro Laptop</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Automated script re-run (run_benchmark_suite.sh); mfusg_gsi_1_8</t>
         </is>
       </c>
     </row>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -2340,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -2413,6 +2413,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="57" t="inlineStr">
@@ -2468,6 +2473,11 @@
           <t>Gaming Laptop</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="57" t="inlineStr">
@@ -2523,6 +2533,11 @@
           <t>Desktop</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="57" t="inlineStr">
@@ -2578,6 +2593,11 @@
           <t>Desktop</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="57" t="inlineStr">
@@ -2633,6 +2653,11 @@
           <t>MacBook Pro Laptop</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="57" t="inlineStr">
@@ -2688,6 +2713,11 @@
           <t>Gaming Laptop</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="1" s="27">
       <c r="A7" s="24" t="inlineStr">
@@ -2748,6 +2778,11 @@
           <t>Incomplete</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="57" t="inlineStr">
@@ -2803,6 +2838,11 @@
           <t>Mac Mini</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="57" t="inlineStr">
@@ -2858,6 +2898,11 @@
           <t>Mac Mini</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="57" t="inlineStr">
@@ -2913,6 +2958,11 @@
           <t>MacBook Pro Laptop</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="57" t="inlineStr">
@@ -2968,6 +3018,11 @@
           <t>MacBook Pro Laptop</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="57" t="inlineStr">
@@ -3023,6 +3078,11 @@
           <t>Mac Mini</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -3079,6 +3139,11 @@
         </is>
       </c>
       <c r="L13" s="27" t="n"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="57" t="inlineStr">
@@ -3134,6 +3199,11 @@
           <t>Deskop Mini Box</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="57" t="inlineStr">
@@ -3189,6 +3259,11 @@
           <t>CPU overclocked by user</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="57" t="inlineStr">
@@ -3244,6 +3319,11 @@
           <t>Gaming Desktop</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="57" t="inlineStr">
@@ -3299,6 +3379,11 @@
           <t>Desktop</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3359,6 +3444,11 @@
           <t>Native ARM64; usgt_180_arm compiled with gfortran via Homebrew GCC</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3419,6 +3509,11 @@
           <t>Native ARM64; usgt_180_arm</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3479,6 +3574,11 @@
           <t>Native ARM64; usgt_180_arm compiled with gfortran via Homebrew GCC</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3537,6 +3637,11 @@
       <c r="L21" t="inlineStr">
         <is>
           <t>Automated script re-run (run_benchmark_suite.sh); mfusg_gsi_1_8</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>automated</t>
         </is>
       </c>
     </row>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -841,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
     <col width="12.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -969,6 +969,11 @@
           <t>M3 Max</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1076,6 +1081,11 @@
           <t>WorkM3</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SGM001</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
@@ -1183,6 +1193,11 @@
           <t>(16c-4.05 GHz)</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(8c-3.2 GHz)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
@@ -1288,6 +1303,11 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>Test20</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Test21</t>
         </is>
       </c>
     </row>
@@ -1355,6 +1375,9 @@
       <c r="U5" t="n">
         <v>5.709317</v>
       </c>
+      <c r="V5" t="n">
+        <v>5.099933</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="54">
       <c r="A6" s="17" t="n">
@@ -1420,6 +1443,9 @@
       <c r="U6" t="n">
         <v>5.7639</v>
       </c>
+      <c r="V6" t="n">
+        <v>5.389</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="54">
       <c r="A7" s="17" t="n">
@@ -1485,6 +1511,9 @@
       <c r="U7" t="n">
         <v>6.011217</v>
       </c>
+      <c r="V7" t="n">
+        <v>5.755717</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="54">
       <c r="A8" s="17" t="n">
@@ -1550,6 +1579,9 @@
       <c r="U8" t="n">
         <v>5.951067</v>
       </c>
+      <c r="V8" t="n">
+        <v>6.399867</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="54">
       <c r="A9" s="17" t="n">
@@ -1615,6 +1647,9 @@
       <c r="U9" t="n">
         <v>5.9857</v>
       </c>
+      <c r="V9" t="n">
+        <v>7.730017</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="54">
       <c r="A10" s="17" t="n">
@@ -1678,6 +1713,9 @@
       <c r="U10" t="n">
         <v>6.013667</v>
       </c>
+      <c r="V10" t="n">
+        <v>9.249582999999999</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="54">
       <c r="A11" s="18" t="n">
@@ -1743,6 +1781,9 @@
       <c r="U11" t="n">
         <v>6.130617</v>
       </c>
+      <c r="V11" t="n">
+        <v>10.87425</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="54">
       <c r="A12" s="17" t="n">
@@ -1808,6 +1849,9 @@
       <c r="U12" t="n">
         <v>6.303217</v>
       </c>
+      <c r="V12" t="n">
+        <v>12.552017</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="54">
       <c r="A13" s="17" t="n">
@@ -1871,6 +1915,9 @@
       <c r="U13" t="n">
         <v>6.508417</v>
       </c>
+      <c r="V13" t="n">
+        <v>14.174833</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="54">
       <c r="A14" s="17" t="n">
@@ -1934,6 +1981,9 @@
       <c r="U14" t="n">
         <v>6.8757</v>
       </c>
+      <c r="V14" t="n">
+        <v>15.798233</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="54">
       <c r="A15" s="17" t="n">
@@ -2000,6 +2050,9 @@
       <c r="U15" t="n">
         <v>7.6243</v>
       </c>
+      <c r="V15" t="n">
+        <v>17.43005</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="54">
       <c r="A16" s="17" t="n">
@@ -2066,6 +2119,9 @@
       <c r="U16" t="n">
         <v>8.267683</v>
       </c>
+      <c r="V16" t="n">
+        <v>19.028917</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="54">
       <c r="A17" s="17" t="n">
@@ -2130,6 +2186,9 @@
       <c r="U17" t="n">
         <v>8.765833000000001</v>
       </c>
+      <c r="V17" t="n">
+        <v>20.642117</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="54">
       <c r="A18" s="17" t="n">
@@ -2196,6 +2255,9 @@
       <c r="U18" t="n">
         <v>9.445633000000001</v>
       </c>
+      <c r="V18" t="n">
+        <v>22.246817</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="54">
       <c r="A19" s="17" t="n">
@@ -2262,6 +2324,9 @@
       <c r="U19" t="n">
         <v>10.121533</v>
       </c>
+      <c r="V19" t="n">
+        <v>23.87075</v>
+      </c>
     </row>
     <row r="20" customFormat="1" s="54">
       <c r="A20" s="17" t="n">
@@ -2326,6 +2391,9 @@
       </c>
       <c r="U20" t="n">
         <v>10.707367</v>
+      </c>
+      <c r="V20" t="n">
+        <v>25.506583</v>
       </c>
     </row>
   </sheetData>
@@ -2340,7 +2408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -3640,6 +3708,71 @@
         </is>
       </c>
       <c r="M21" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Test21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>roh@sgmco.cl</t>
+        </is>
+      </c>
+      <c r="C22" s="61" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SGM001</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>(8c-3.2 GHz)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ARM64 (gfortran)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Mac Mini</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Native ARM64; usgt_180_arm; automated script</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>automated</t>
         </is>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -2878,7 +2878,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SGM001 </t>
+          <t>SGM001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SGM005 </t>
+          <t>SGM005</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESI </t>
+          <t>ESI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -841,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
     <col width="12.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -974,6 +974,11 @@
           <t>M1</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>M2 Pro</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1086,6 +1091,11 @@
           <t>SGM001</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>WorkM2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
@@ -1198,6 +1208,11 @@
           <t>(8c-3.2 GHz)</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>(12c-3.48GHz)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
@@ -1308,6 +1323,11 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>Test21</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Test22</t>
         </is>
       </c>
     </row>
@@ -1378,6 +1398,9 @@
       <c r="V5" t="n">
         <v>5.099933</v>
       </c>
+      <c r="W5" t="n">
+        <v>4.9245</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="54">
       <c r="A6" s="17" t="n">
@@ -1446,6 +1469,9 @@
       <c r="V6" t="n">
         <v>5.389</v>
       </c>
+      <c r="W6" t="n">
+        <v>5.012633</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="54">
       <c r="A7" s="17" t="n">
@@ -1514,6 +1540,9 @@
       <c r="V7" t="n">
         <v>5.755717</v>
       </c>
+      <c r="W7" t="n">
+        <v>5.111433</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="54">
       <c r="A8" s="17" t="n">
@@ -1582,6 +1611,9 @@
       <c r="V8" t="n">
         <v>6.399867</v>
       </c>
+      <c r="W8" t="n">
+        <v>5.1694</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="54">
       <c r="A9" s="17" t="n">
@@ -1650,6 +1682,9 @@
       <c r="V9" t="n">
         <v>7.730017</v>
       </c>
+      <c r="W9" t="n">
+        <v>5.35155</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="54">
       <c r="A10" s="17" t="n">
@@ -1716,6 +1751,9 @@
       <c r="V10" t="n">
         <v>9.249582999999999</v>
       </c>
+      <c r="W10" t="n">
+        <v>5.435383</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="54">
       <c r="A11" s="18" t="n">
@@ -1784,6 +1822,9 @@
       <c r="V11" t="n">
         <v>10.87425</v>
       </c>
+      <c r="W11" t="n">
+        <v>5.867167</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="54">
       <c r="A12" s="17" t="n">
@@ -1852,6 +1893,9 @@
       <c r="V12" t="n">
         <v>12.552017</v>
       </c>
+      <c r="W12" t="n">
+        <v>5.773</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="54">
       <c r="A13" s="17" t="n">
@@ -1918,6 +1962,9 @@
       <c r="V13" t="n">
         <v>14.174833</v>
       </c>
+      <c r="W13" t="n">
+        <v>6.203467</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="54">
       <c r="A14" s="17" t="n">
@@ -1984,6 +2031,9 @@
       <c r="V14" t="n">
         <v>15.798233</v>
       </c>
+      <c r="W14" t="n">
+        <v>6.63255</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="54">
       <c r="A15" s="17" t="n">
@@ -2053,6 +2103,9 @@
       <c r="V15" t="n">
         <v>17.43005</v>
       </c>
+      <c r="W15" t="n">
+        <v>7.125233</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="54">
       <c r="A16" s="17" t="n">
@@ -2122,6 +2175,9 @@
       <c r="V16" t="n">
         <v>19.028917</v>
       </c>
+      <c r="W16" t="n">
+        <v>7.5704</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="54">
       <c r="A17" s="17" t="n">
@@ -2189,6 +2245,9 @@
       <c r="V17" t="n">
         <v>20.642117</v>
       </c>
+      <c r="W17" t="n">
+        <v>8.410717</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="54">
       <c r="A18" s="17" t="n">
@@ -2258,6 +2317,9 @@
       <c r="V18" t="n">
         <v>22.246817</v>
       </c>
+      <c r="W18" t="n">
+        <v>9.02685</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="54">
       <c r="A19" s="17" t="n">
@@ -2327,6 +2389,9 @@
       <c r="V19" t="n">
         <v>23.87075</v>
       </c>
+      <c r="W19" t="n">
+        <v>9.576333</v>
+      </c>
     </row>
     <row r="20" customFormat="1" s="54">
       <c r="A20" s="17" t="n">
@@ -2394,6 +2459,9 @@
       </c>
       <c r="V20" t="n">
         <v>25.506583</v>
+      </c>
+      <c r="W20" t="n">
+        <v>10.207567</v>
       </c>
     </row>
   </sheetData>
@@ -2408,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -3773,6 +3841,71 @@
         </is>
       </c>
       <c r="M22" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Test22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roh@sgmco.cl</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M2 Pro</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WorkM2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>(12c-3.48GHz)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ARM64 (gfortran)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>MacBook Pro Laptop</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Native ARM64; usgt_180_arm; automated script</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>automated</t>
         </is>

--- a/Runtimes/ByscayneMode_Benchmarks.xlsx
+++ b/Runtimes/ByscayneMode_Benchmarks.xlsx
@@ -841,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
     <col width="12.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -979,6 +979,11 @@
           <t>M2 Pro</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1096,6 +1101,11 @@
           <t>WorkM2</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>SGM005</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
@@ -1213,6 +1223,11 @@
           <t>(12c-3.48GHz)</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>(8c-3.49 GHz)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="47" t="inlineStr">
@@ -1328,6 +1343,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>Test22</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Test23</t>
         </is>
       </c>
     </row>
@@ -1401,6 +1421,9 @@
       <c r="W5" t="n">
         <v>4.9245</v>
       </c>
+      <c r="X5" t="n">
+        <v>4.79765</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="54">
       <c r="A6" s="17" t="n">
@@ -1472,6 +1495,9 @@
       <c r="W6" t="n">
         <v>5.012633</v>
       </c>
+      <c r="X6" t="n">
+        <v>5.149467</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="54">
       <c r="A7" s="17" t="n">
@@ -1543,6 +1569,9 @@
       <c r="W7" t="n">
         <v>5.111433</v>
       </c>
+      <c r="X7" t="n">
+        <v>5.50225</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="54">
       <c r="A8" s="17" t="n">
@@ -1614,6 +1643,9 @@
       <c r="W8" t="n">
         <v>5.1694</v>
       </c>
+      <c r="X8" t="n">
+        <v>5.8126</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="54">
       <c r="A9" s="17" t="n">
@@ -1685,6 +1717,9 @@
       <c r="W9" t="n">
         <v>5.35155</v>
       </c>
+      <c r="X9" t="n">
+        <v>6.67115</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="54">
       <c r="A10" s="17" t="n">
@@ -1754,6 +1789,9 @@
       <c r="W10" t="n">
         <v>5.435383</v>
       </c>
+      <c r="X10" t="n">
+        <v>7.699667</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="54">
       <c r="A11" s="18" t="n">
@@ -1825,6 +1863,9 @@
       <c r="W11" t="n">
         <v>5.867167</v>
       </c>
+      <c r="X11" t="n">
+        <v>8.978717</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="54">
       <c r="A12" s="17" t="n">
@@ -1896,6 +1937,9 @@
       <c r="W12" t="n">
         <v>5.773</v>
       </c>
+      <c r="X12" t="n">
+        <v>10.343867</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="54">
       <c r="A13" s="17" t="n">
@@ -1965,6 +2009,9 @@
       <c r="W13" t="n">
         <v>6.203467</v>
       </c>
+      <c r="X13" t="n">
+        <v>11.649117</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="54">
       <c r="A14" s="17" t="n">
@@ -2034,6 +2081,9 @@
       <c r="W14" t="n">
         <v>6.63255</v>
       </c>
+      <c r="X14" t="n">
+        <v>13.0017</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="54">
       <c r="A15" s="17" t="n">
@@ -2106,6 +2156,9 @@
       <c r="W15" t="n">
         <v>7.125233</v>
       </c>
+      <c r="X15" t="n">
+        <v>14.335783</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="54">
       <c r="A16" s="17" t="n">
@@ -2178,6 +2231,9 @@
       <c r="W16" t="n">
         <v>7.5704</v>
       </c>
+      <c r="X16" t="n">
+        <v>15.682383</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="54">
       <c r="A17" s="17" t="n">
@@ -2248,6 +2304,9 @@
       <c r="W17" t="n">
         <v>8.410717</v>
       </c>
+      <c r="X17" t="n">
+        <v>17.007183</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="54">
       <c r="A18" s="17" t="n">
@@ -2320,6 +2379,9 @@
       <c r="W18" t="n">
         <v>9.02685</v>
       </c>
+      <c r="X18" t="n">
+        <v>18.312267</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="54">
       <c r="A19" s="17" t="n">
@@ -2392,6 +2454,9 @@
       <c r="W19" t="n">
         <v>9.576333</v>
       </c>
+      <c r="X19" t="n">
+        <v>19.64135</v>
+      </c>
     </row>
     <row r="20" customFormat="1" s="54">
       <c r="A20" s="17" t="n">
@@ -2462,6 +2527,9 @@
       </c>
       <c r="W20" t="n">
         <v>10.207567</v>
+      </c>
+      <c r="X20" t="n">
+        <v>20.973967</v>
       </c>
     </row>
   </sheetData>
@@ -2476,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" min="2" max="2"/>
@@ -3906,6 +3974,71 @@
         </is>
       </c>
       <c r="M23" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Test23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>roh@sgmco.cl</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>macOS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SGM005</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>(8c-3.49 GHz)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ARM64 (gfortran)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Mac Mini</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Native ARM64; usgt_180_arm; automated script</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
